--- a/data/bom_master.xlsx
+++ b/data/bom_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\업무\36. 개발노트\원료비원인분석\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A58854B-34CD-4AFD-9A59-EE6C322A4225}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FA3ED7C-E470-495D-9C2D-3E17BC6759FD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7845" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -779,9 +779,6 @@
     <t>마리골드 추출물</t>
   </si>
   <si>
-    <t>밥이보약 튼튼한 관절 액티브 DOG</t>
-  </si>
-  <si>
     <t>1091008</t>
   </si>
   <si>
@@ -1032,6 +1029,9 @@
   </si>
   <si>
     <t>소고기 분쇄육 (더 리얼)</t>
+  </si>
+  <si>
+    <t>밥이보약 DOG 액티브 모빌리티</t>
   </si>
 </sst>
 </file>
@@ -1438,6 +1438,7 @@
   <dimension ref="A1:E1876"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="42.625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.25" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="49.75" bestFit="1" customWidth="1"/>
   </cols>
@@ -3063,7 +3064,7 @@
         <v>1010300</v>
       </c>
       <c r="D116" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E116">
         <v>40</v>
@@ -8131,7 +8132,7 @@
         <v>1010301</v>
       </c>
       <c r="D478" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E478">
         <v>14.7638</v>
@@ -8663,7 +8664,7 @@
         <v>1010301</v>
       </c>
       <c r="D516" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E516">
         <v>15.356199999999999</v>
@@ -24267,7 +24268,7 @@
     </row>
     <row r="1631" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1631" t="s">
-        <v>252</v>
+        <v>336</v>
       </c>
       <c r="C1631" s="2">
         <v>1010101</v>
@@ -24281,7 +24282,7 @@
     </row>
     <row r="1632" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1632" t="s">
-        <v>252</v>
+        <v>336</v>
       </c>
       <c r="C1632" s="2">
         <v>1050801</v>
@@ -24295,7 +24296,7 @@
     </row>
     <row r="1633" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1633" t="s">
-        <v>252</v>
+        <v>336</v>
       </c>
       <c r="C1633" s="2">
         <v>1030501</v>
@@ -24309,7 +24310,7 @@
     </row>
     <row r="1634" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1634" t="s">
-        <v>252</v>
+        <v>336</v>
       </c>
       <c r="C1634" s="2">
         <v>1030601</v>
@@ -24323,7 +24324,7 @@
     </row>
     <row r="1635" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1635" t="s">
-        <v>252</v>
+        <v>336</v>
       </c>
       <c r="C1635" s="2">
         <v>1050711</v>
@@ -24337,7 +24338,7 @@
     </row>
     <row r="1636" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1636" t="s">
-        <v>252</v>
+        <v>336</v>
       </c>
       <c r="C1636" s="2">
         <v>1050901</v>
@@ -24351,7 +24352,7 @@
     </row>
     <row r="1637" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1637" t="s">
-        <v>252</v>
+        <v>336</v>
       </c>
       <c r="C1637" s="2">
         <v>1010501</v>
@@ -24365,7 +24366,7 @@
     </row>
     <row r="1638" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1638" t="s">
-        <v>252</v>
+        <v>336</v>
       </c>
       <c r="C1638" s="2">
         <v>1060101</v>
@@ -24379,7 +24380,7 @@
     </row>
     <row r="1639" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1639" t="s">
-        <v>252</v>
+        <v>336</v>
       </c>
       <c r="C1639" s="2">
         <v>1090602</v>
@@ -24393,7 +24394,7 @@
     </row>
     <row r="1640" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1640" t="s">
-        <v>252</v>
+        <v>336</v>
       </c>
       <c r="C1640" s="2">
         <v>1080401</v>
@@ -24407,7 +24408,7 @@
     </row>
     <row r="1641" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1641" t="s">
-        <v>252</v>
+        <v>336</v>
       </c>
       <c r="C1641" s="2">
         <v>1020301</v>
@@ -24421,7 +24422,7 @@
     </row>
     <row r="1642" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1642" t="s">
-        <v>252</v>
+        <v>336</v>
       </c>
       <c r="C1642" s="2">
         <v>1020401</v>
@@ -24435,7 +24436,7 @@
     </row>
     <row r="1643" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1643" t="s">
-        <v>252</v>
+        <v>336</v>
       </c>
       <c r="C1643" s="2">
         <v>1010701</v>
@@ -24449,7 +24450,7 @@
     </row>
     <row r="1644" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1644" t="s">
-        <v>252</v>
+        <v>336</v>
       </c>
       <c r="C1644" s="2">
         <v>1080501</v>
@@ -24463,7 +24464,7 @@
     </row>
     <row r="1645" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1645" t="s">
-        <v>252</v>
+        <v>336</v>
       </c>
       <c r="C1645" s="2">
         <v>1080201</v>
@@ -24477,7 +24478,7 @@
     </row>
     <row r="1646" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1646" t="s">
-        <v>252</v>
+        <v>336</v>
       </c>
       <c r="C1646" s="2">
         <v>1050541</v>
@@ -24491,7 +24492,7 @@
     </row>
     <row r="1647" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1647" t="s">
-        <v>252</v>
+        <v>336</v>
       </c>
       <c r="C1647" s="2">
         <v>1050721</v>
@@ -24505,7 +24506,7 @@
     </row>
     <row r="1648" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1648" t="s">
-        <v>252</v>
+        <v>336</v>
       </c>
       <c r="C1648" s="2">
         <v>1090401</v>
@@ -24519,7 +24520,7 @@
     </row>
     <row r="1649" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1649" t="s">
-        <v>252</v>
+        <v>336</v>
       </c>
       <c r="C1649" s="2">
         <v>1080301</v>
@@ -24533,7 +24534,7 @@
     </row>
     <row r="1650" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1650" t="s">
-        <v>252</v>
+        <v>336</v>
       </c>
       <c r="C1650" s="2">
         <v>1070401</v>
@@ -24547,7 +24548,7 @@
     </row>
     <row r="1651" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1651" t="s">
-        <v>252</v>
+        <v>336</v>
       </c>
       <c r="C1651" s="2">
         <v>1070501</v>
@@ -24561,7 +24562,7 @@
     </row>
     <row r="1652" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1652" t="s">
-        <v>252</v>
+        <v>336</v>
       </c>
       <c r="C1652" s="2">
         <v>1080101</v>
@@ -24575,7 +24576,7 @@
     </row>
     <row r="1653" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1653" t="s">
-        <v>252</v>
+        <v>336</v>
       </c>
       <c r="C1653" s="2">
         <v>1080602</v>
@@ -24589,7 +24590,7 @@
     </row>
     <row r="1654" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1654" t="s">
-        <v>252</v>
+        <v>336</v>
       </c>
       <c r="C1654" s="2">
         <v>1090701</v>
@@ -24603,7 +24604,7 @@
     </row>
     <row r="1655" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1655" t="s">
-        <v>252</v>
+        <v>336</v>
       </c>
       <c r="C1655" s="2">
         <v>1080702</v>
@@ -24617,13 +24618,13 @@
     </row>
     <row r="1656" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1656" t="s">
-        <v>252</v>
+        <v>336</v>
       </c>
       <c r="C1656" s="2">
         <v>1091008</v>
       </c>
       <c r="D1656" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E1656">
         <v>6.7400000000000002E-2</v>
@@ -24631,7 +24632,7 @@
     </row>
     <row r="1657" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1657" t="s">
-        <v>252</v>
+        <v>336</v>
       </c>
       <c r="C1657" s="2">
         <v>1050102</v>
@@ -24645,7 +24646,7 @@
     </row>
     <row r="1658" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1658" t="s">
-        <v>252</v>
+        <v>336</v>
       </c>
       <c r="C1658" s="2">
         <v>1090321</v>
@@ -24659,7 +24660,7 @@
     </row>
     <row r="1659" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1659" t="s">
-        <v>252</v>
+        <v>336</v>
       </c>
       <c r="C1659" s="2">
         <v>1090201</v>
@@ -24673,7 +24674,7 @@
     </row>
     <row r="1660" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1660" t="s">
-        <v>252</v>
+        <v>336</v>
       </c>
       <c r="C1660" s="2">
         <v>1070101</v>
@@ -24687,7 +24688,7 @@
     </row>
     <row r="1661" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1661" t="s">
-        <v>252</v>
+        <v>336</v>
       </c>
       <c r="C1661" s="2">
         <v>1050601</v>
@@ -24701,7 +24702,7 @@
     </row>
     <row r="1662" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1662" t="s">
-        <v>252</v>
+        <v>336</v>
       </c>
       <c r="C1662" s="2">
         <v>1090301</v>
@@ -24715,7 +24716,7 @@
     </row>
     <row r="1663" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1663" t="s">
-        <v>252</v>
+        <v>336</v>
       </c>
       <c r="C1663" s="2">
         <v>1090211</v>
@@ -24729,7 +24730,7 @@
     </row>
     <row r="1664" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1664" t="s">
-        <v>252</v>
+        <v>336</v>
       </c>
       <c r="C1664" s="2">
         <v>1090311</v>
@@ -24743,7 +24744,7 @@
     </row>
     <row r="1665" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1665" t="s">
-        <v>252</v>
+        <v>336</v>
       </c>
       <c r="C1665" s="2">
         <v>1090411</v>
@@ -24757,7 +24758,7 @@
     </row>
     <row r="1666" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1666" t="s">
-        <v>252</v>
+        <v>336</v>
       </c>
       <c r="C1666" s="2">
         <v>1070301</v>
@@ -24771,13 +24772,13 @@
     </row>
     <row r="1667" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1667" t="s">
-        <v>252</v>
+        <v>336</v>
       </c>
       <c r="C1667" s="2">
         <v>1091009</v>
       </c>
       <c r="D1667" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E1667">
         <v>1.1900000000000001E-2</v>
@@ -24785,7 +24786,7 @@
     </row>
     <row r="1668" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1668" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C1668" s="2">
         <v>1010101</v>
@@ -24799,7 +24800,7 @@
     </row>
     <row r="1669" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1669" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C1669" s="2">
         <v>1030201</v>
@@ -24813,7 +24814,7 @@
     </row>
     <row r="1670" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1670" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C1670" s="2">
         <v>1050901</v>
@@ -24827,7 +24828,7 @@
     </row>
     <row r="1671" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1671" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C1671" s="2">
         <v>1050702</v>
@@ -24841,7 +24842,7 @@
     </row>
     <row r="1672" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1672" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C1672" s="2">
         <v>1050801</v>
@@ -24855,7 +24856,7 @@
     </row>
     <row r="1673" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1673" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C1673" s="2">
         <v>1040201</v>
@@ -24869,7 +24870,7 @@
     </row>
     <row r="1674" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1674" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C1674" s="2">
         <v>1060101</v>
@@ -24883,7 +24884,7 @@
     </row>
     <row r="1675" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1675" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C1675" s="2">
         <v>1090602</v>
@@ -24897,13 +24898,13 @@
     </row>
     <row r="1676" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1676" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C1676" s="2">
         <v>6000002</v>
       </c>
       <c r="D1676" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E1676">
         <v>3</v>
@@ -24911,13 +24912,13 @@
     </row>
     <row r="1677" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1677" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C1677" s="2">
         <v>1050571</v>
       </c>
       <c r="D1677" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E1677">
         <v>2.9</v>
@@ -24925,7 +24926,7 @@
     </row>
     <row r="1678" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1678" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C1678" s="2">
         <v>1080401</v>
@@ -24939,7 +24940,7 @@
     </row>
     <row r="1679" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1679" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C1679" s="2">
         <v>1090401</v>
@@ -24953,7 +24954,7 @@
     </row>
     <row r="1680" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1680" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C1680" s="2">
         <v>1020101</v>
@@ -24967,7 +24968,7 @@
     </row>
     <row r="1681" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1681" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C1681" s="2">
         <v>1020201</v>
@@ -24981,7 +24982,7 @@
     </row>
     <row r="1682" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1682" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C1682" s="2">
         <v>1050102</v>
@@ -24995,7 +24996,7 @@
     </row>
     <row r="1683" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1683" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C1683" s="2">
         <v>1090551</v>
@@ -25009,7 +25010,7 @@
     </row>
     <row r="1684" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1684" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C1684" s="2">
         <v>1080301</v>
@@ -25023,7 +25024,7 @@
     </row>
     <row r="1685" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1685" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C1685" s="2">
         <v>1080501</v>
@@ -25037,7 +25038,7 @@
     </row>
     <row r="1686" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1686" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C1686" s="2">
         <v>1080201</v>
@@ -25051,13 +25052,13 @@
     </row>
     <row r="1687" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1687" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C1687" s="2">
         <v>1050551</v>
       </c>
       <c r="D1687" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E1687">
         <v>0.3</v>
@@ -25065,13 +25066,13 @@
     </row>
     <row r="1688" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1688" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C1688" s="2">
         <v>1050561</v>
       </c>
       <c r="D1688" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E1688">
         <v>0.3</v>
@@ -25079,7 +25080,7 @@
     </row>
     <row r="1689" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1689" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C1689" s="2">
         <v>1070401</v>
@@ -25093,7 +25094,7 @@
     </row>
     <row r="1690" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1690" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C1690" s="2">
         <v>1080101</v>
@@ -25107,7 +25108,7 @@
     </row>
     <row r="1691" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1691" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C1691" s="2">
         <v>1050601</v>
@@ -25121,7 +25122,7 @@
     </row>
     <row r="1692" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1692" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C1692" s="2">
         <v>1090321</v>
@@ -25135,7 +25136,7 @@
     </row>
     <row r="1693" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1693" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C1693" s="2">
         <v>1080702</v>
@@ -25149,7 +25150,7 @@
     </row>
     <row r="1694" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1694" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C1694" s="2">
         <v>1080602</v>
@@ -25163,7 +25164,7 @@
     </row>
     <row r="1695" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1695" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C1695" s="2">
         <v>1070501</v>
@@ -25177,7 +25178,7 @@
     </row>
     <row r="1696" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1696" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C1696" s="2">
         <v>1070101</v>
@@ -25191,7 +25192,7 @@
     </row>
     <row r="1697" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1697" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C1697" s="2">
         <v>1090301</v>
@@ -25205,7 +25206,7 @@
     </row>
     <row r="1698" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1698" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C1698" s="2">
         <v>1090311</v>
@@ -25219,7 +25220,7 @@
     </row>
     <row r="1699" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1699" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C1699" s="2">
         <v>1070301</v>
@@ -25233,7 +25234,7 @@
     </row>
     <row r="1700" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1700" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C1700" s="2">
         <v>1010101</v>
@@ -25247,7 +25248,7 @@
     </row>
     <row r="1701" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1701" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C1701" s="2">
         <v>1050702</v>
@@ -25261,7 +25262,7 @@
     </row>
     <row r="1702" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1702" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C1702" s="2">
         <v>1050901</v>
@@ -25275,7 +25276,7 @@
     </row>
     <row r="1703" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1703" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C1703" s="2">
         <v>1030201</v>
@@ -25289,7 +25290,7 @@
     </row>
     <row r="1704" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1704" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C1704" s="2">
         <v>1040201</v>
@@ -25303,7 +25304,7 @@
     </row>
     <row r="1705" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1705" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C1705" s="2">
         <v>1090602</v>
@@ -25317,7 +25318,7 @@
     </row>
     <row r="1706" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1706" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C1706" s="2">
         <v>1020201</v>
@@ -25331,7 +25332,7 @@
     </row>
     <row r="1707" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1707" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C1707" s="2">
         <v>1050801</v>
@@ -25345,7 +25346,7 @@
     </row>
     <row r="1708" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1708" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C1708" s="2">
         <v>6000002</v>
@@ -25359,13 +25360,13 @@
     </row>
     <row r="1709" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1709" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C1709" s="2">
         <v>1050571</v>
       </c>
       <c r="D1709" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E1709">
         <v>2.9</v>
@@ -25373,7 +25374,7 @@
     </row>
     <row r="1710" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1710" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C1710" s="2">
         <v>1060101</v>
@@ -25387,7 +25388,7 @@
     </row>
     <row r="1711" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1711" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C1711" s="2">
         <v>1080401</v>
@@ -25401,7 +25402,7 @@
     </row>
     <row r="1712" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1712" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C1712" s="2">
         <v>1090401</v>
@@ -25415,7 +25416,7 @@
     </row>
     <row r="1713" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1713" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C1713" s="2">
         <v>1020101</v>
@@ -25429,7 +25430,7 @@
     </row>
     <row r="1714" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1714" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C1714" s="2">
         <v>1080301</v>
@@ -25443,7 +25444,7 @@
     </row>
     <row r="1715" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1715" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C1715" s="2">
         <v>1050102</v>
@@ -25457,7 +25458,7 @@
     </row>
     <row r="1716" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1716" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C1716" s="2">
         <v>1080501</v>
@@ -25471,7 +25472,7 @@
     </row>
     <row r="1717" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1717" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C1717" s="2">
         <v>1090551</v>
@@ -25485,7 +25486,7 @@
     </row>
     <row r="1718" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1718" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C1718" s="2">
         <v>1080201</v>
@@ -25499,13 +25500,13 @@
     </row>
     <row r="1719" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1719" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C1719" s="2">
         <v>1050551</v>
       </c>
       <c r="D1719" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E1719">
         <v>0.3</v>
@@ -25513,13 +25514,13 @@
     </row>
     <row r="1720" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1720" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C1720" s="2">
         <v>1050591</v>
       </c>
       <c r="D1720" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E1720">
         <v>0.3</v>
@@ -25527,7 +25528,7 @@
     </row>
     <row r="1721" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1721" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C1721" s="2">
         <v>1070401</v>
@@ -25541,7 +25542,7 @@
     </row>
     <row r="1722" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1722" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C1722" s="2">
         <v>1080101</v>
@@ -25555,7 +25556,7 @@
     </row>
     <row r="1723" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1723" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C1723" s="2">
         <v>1070501</v>
@@ -25569,7 +25570,7 @@
     </row>
     <row r="1724" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1724" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C1724" s="2">
         <v>1080602</v>
@@ -25583,7 +25584,7 @@
     </row>
     <row r="1725" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1725" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C1725" s="2">
         <v>1080702</v>
@@ -25597,7 +25598,7 @@
     </row>
     <row r="1726" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1726" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C1726" s="2">
         <v>1050601</v>
@@ -25611,7 +25612,7 @@
     </row>
     <row r="1727" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1727" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C1727" s="2">
         <v>1090321</v>
@@ -25625,7 +25626,7 @@
     </row>
     <row r="1728" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1728" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C1728" s="2">
         <v>1070101</v>
@@ -25639,7 +25640,7 @@
     </row>
     <row r="1729" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1729" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C1729" s="2">
         <v>1090311</v>
@@ -25653,7 +25654,7 @@
     </row>
     <row r="1730" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1730" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C1730" s="2">
         <v>1090301</v>
@@ -25667,7 +25668,7 @@
     </row>
     <row r="1731" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1731" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C1731" s="2">
         <v>1070301</v>
@@ -25681,7 +25682,7 @@
     </row>
     <row r="1732" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1732" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C1732" s="2">
         <v>1010401</v>
@@ -25695,7 +25696,7 @@
     </row>
     <row r="1733" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1733" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C1733" s="2">
         <v>1050901</v>
@@ -25709,7 +25710,7 @@
     </row>
     <row r="1734" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1734" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C1734" s="2">
         <v>1030201</v>
@@ -25723,7 +25724,7 @@
     </row>
     <row r="1735" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1735" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C1735" s="2">
         <v>1050702</v>
@@ -25737,7 +25738,7 @@
     </row>
     <row r="1736" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1736" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C1736" s="2">
         <v>1040201</v>
@@ -25751,7 +25752,7 @@
     </row>
     <row r="1737" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1737" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C1737" s="2">
         <v>1050801</v>
@@ -25765,7 +25766,7 @@
     </row>
     <row r="1738" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1738" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C1738" s="2">
         <v>1060101</v>
@@ -25779,7 +25780,7 @@
     </row>
     <row r="1739" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1739" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C1739" s="2">
         <v>1090602</v>
@@ -25793,7 +25794,7 @@
     </row>
     <row r="1740" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1740" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C1740" s="2">
         <v>1020201</v>
@@ -25807,13 +25808,13 @@
     </row>
     <row r="1741" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1741" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C1741" s="2">
         <v>6000002</v>
       </c>
       <c r="D1741" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E1741">
         <v>3</v>
@@ -25821,13 +25822,13 @@
     </row>
     <row r="1742" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1742" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C1742" s="2">
         <v>1050581</v>
       </c>
       <c r="D1742" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E1742">
         <v>2.9</v>
@@ -25835,7 +25836,7 @@
     </row>
     <row r="1743" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1743" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C1743" s="2">
         <v>1080401</v>
@@ -25849,7 +25850,7 @@
     </row>
     <row r="1744" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1744" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C1744" s="2">
         <v>1020101</v>
@@ -25863,7 +25864,7 @@
     </row>
     <row r="1745" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1745" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C1745" s="2">
         <v>1090401</v>
@@ -25877,7 +25878,7 @@
     </row>
     <row r="1746" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1746" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C1746" s="2">
         <v>1080301</v>
@@ -25891,7 +25892,7 @@
     </row>
     <row r="1747" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1747" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C1747" s="2">
         <v>1050102</v>
@@ -25905,7 +25906,7 @@
     </row>
     <row r="1748" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1748" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C1748" s="2">
         <v>1080501</v>
@@ -25919,7 +25920,7 @@
     </row>
     <row r="1749" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1749" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C1749" s="2">
         <v>1090551</v>
@@ -25933,7 +25934,7 @@
     </row>
     <row r="1750" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1750" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C1750" s="2">
         <v>1080201</v>
@@ -25947,13 +25948,13 @@
     </row>
     <row r="1751" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1751" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C1751" s="2">
         <v>1050551</v>
       </c>
       <c r="D1751" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E1751">
         <v>0.3</v>
@@ -25961,13 +25962,13 @@
     </row>
     <row r="1752" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1752" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C1752" s="2">
         <v>1050591</v>
       </c>
       <c r="D1752" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E1752">
         <v>0.3</v>
@@ -25975,7 +25976,7 @@
     </row>
     <row r="1753" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1753" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C1753" s="2">
         <v>1070401</v>
@@ -25989,7 +25990,7 @@
     </row>
     <row r="1754" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1754" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C1754" s="2">
         <v>1080101</v>
@@ -26003,7 +26004,7 @@
     </row>
     <row r="1755" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1755" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C1755" s="2">
         <v>1070501</v>
@@ -26017,7 +26018,7 @@
     </row>
     <row r="1756" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1756" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C1756" s="2">
         <v>1080602</v>
@@ -26031,7 +26032,7 @@
     </row>
     <row r="1757" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1757" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C1757" s="2">
         <v>1080702</v>
@@ -26045,7 +26046,7 @@
     </row>
     <row r="1758" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1758" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C1758" s="2">
         <v>1050601</v>
@@ -26059,7 +26060,7 @@
     </row>
     <row r="1759" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1759" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C1759" s="2">
         <v>1090321</v>
@@ -26073,7 +26074,7 @@
     </row>
     <row r="1760" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1760" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C1760" s="2">
         <v>1070101</v>
@@ -26087,7 +26088,7 @@
     </row>
     <row r="1761" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1761" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C1761" s="2">
         <v>1090311</v>
@@ -26101,7 +26102,7 @@
     </row>
     <row r="1762" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1762" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C1762" s="2">
         <v>1090301</v>
@@ -26115,7 +26116,7 @@
     </row>
     <row r="1763" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1763" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C1763" s="2">
         <v>1070301</v>
@@ -26129,7 +26130,7 @@
     </row>
     <row r="1764" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1764" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C1764" s="2">
         <v>1010401</v>
@@ -26143,7 +26144,7 @@
     </row>
     <row r="1765" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1765" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C1765" s="2">
         <v>1010101</v>
@@ -26157,7 +26158,7 @@
     </row>
     <row r="1766" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1766" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C1766" s="2">
         <v>1050711</v>
@@ -26171,7 +26172,7 @@
     </row>
     <row r="1767" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1767" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C1767" s="2">
         <v>1050801</v>
@@ -26185,7 +26186,7 @@
     </row>
     <row r="1768" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1768" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C1768" s="2">
         <v>1040201</v>
@@ -26199,7 +26200,7 @@
     </row>
     <row r="1769" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1769" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C1769" s="2">
         <v>1050901</v>
@@ -26213,7 +26214,7 @@
     </row>
     <row r="1770" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1770" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C1770" s="2">
         <v>1060101</v>
@@ -26227,7 +26228,7 @@
     </row>
     <row r="1771" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1771" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C1771" s="2">
         <v>1010501</v>
@@ -26241,7 +26242,7 @@
     </row>
     <row r="1772" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1772" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C1772" s="2">
         <v>1020201</v>
@@ -26255,7 +26256,7 @@
     </row>
     <row r="1773" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1773" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C1773" s="2">
         <v>1090602</v>
@@ -26269,7 +26270,7 @@
     </row>
     <row r="1774" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1774" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C1774" s="2">
         <v>1050701</v>
@@ -26283,7 +26284,7 @@
     </row>
     <row r="1775" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1775" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C1775" s="2">
         <v>1050721</v>
@@ -26297,7 +26298,7 @@
     </row>
     <row r="1776" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1776" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C1776" s="2">
         <v>1020301</v>
@@ -26311,7 +26312,7 @@
     </row>
     <row r="1777" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1777" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C1777" s="2">
         <v>1090401</v>
@@ -26325,7 +26326,7 @@
     </row>
     <row r="1778" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1778" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C1778" s="2">
         <v>1080411</v>
@@ -26339,7 +26340,7 @@
     </row>
     <row r="1779" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1779" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C1779" s="2">
         <v>1020101</v>
@@ -26353,7 +26354,7 @@
     </row>
     <row r="1780" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1780" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C1780" s="2">
         <v>1090611</v>
@@ -26367,7 +26368,7 @@
     </row>
     <row r="1781" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1781" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C1781" s="2">
         <v>1080301</v>
@@ -26381,7 +26382,7 @@
     </row>
     <row r="1782" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1782" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C1782" s="2">
         <v>1080201</v>
@@ -26395,7 +26396,7 @@
     </row>
     <row r="1783" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1783" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C1783" s="2">
         <v>1080501</v>
@@ -26409,7 +26410,7 @@
     </row>
     <row r="1784" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1784" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C1784" s="2">
         <v>1090901</v>
@@ -26423,7 +26424,7 @@
     </row>
     <row r="1785" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1785" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C1785" s="2">
         <v>1080101</v>
@@ -26437,7 +26438,7 @@
     </row>
     <row r="1786" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1786" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C1786" s="2">
         <v>1090551</v>
@@ -26451,7 +26452,7 @@
     </row>
     <row r="1787" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1787" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C1787" s="2">
         <v>1070401</v>
@@ -26465,7 +26466,7 @@
     </row>
     <row r="1788" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1788" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C1788" s="2">
         <v>1050102</v>
@@ -26479,7 +26480,7 @@
     </row>
     <row r="1789" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1789" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C1789" s="2">
         <v>1070101</v>
@@ -26493,7 +26494,7 @@
     </row>
     <row r="1790" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1790" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C1790" s="2">
         <v>1080702</v>
@@ -26507,7 +26508,7 @@
     </row>
     <row r="1791" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1791" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C1791" s="2">
         <v>1080602</v>
@@ -26521,7 +26522,7 @@
     </row>
     <row r="1792" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1792" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C1792" s="2">
         <v>1070501</v>
@@ -26535,7 +26536,7 @@
     </row>
     <row r="1793" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1793" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C1793" s="2">
         <v>1050601</v>
@@ -26549,7 +26550,7 @@
     </row>
     <row r="1794" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1794" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C1794" s="2">
         <v>1091010</v>
@@ -26563,13 +26564,13 @@
     </row>
     <row r="1795" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1795" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C1795" s="2">
         <v>1091012</v>
       </c>
       <c r="D1795" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E1795">
         <v>0.10199999999999999</v>
@@ -26577,7 +26578,7 @@
     </row>
     <row r="1796" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1796" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C1796" s="2">
         <v>1090321</v>
@@ -26591,7 +26592,7 @@
     </row>
     <row r="1797" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1797" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C1797" s="2">
         <v>1090421</v>
@@ -26605,7 +26606,7 @@
     </row>
     <row r="1798" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1798" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C1798" s="2">
         <v>1090311</v>
@@ -26619,7 +26620,7 @@
     </row>
     <row r="1799" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1799" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C1799" s="2">
         <v>1060412</v>
@@ -26633,7 +26634,7 @@
     </row>
     <row r="1800" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1800" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C1800" s="2">
         <v>1090201</v>
@@ -26647,13 +26648,13 @@
     </row>
     <row r="1801" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1801" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C1801" s="2">
         <v>1091013</v>
       </c>
       <c r="D1801" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E1801">
         <v>5.0999999999999997E-2</v>
@@ -26661,7 +26662,7 @@
     </row>
     <row r="1802" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1802" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C1802" s="2">
         <v>1090301</v>
@@ -26675,7 +26676,7 @@
     </row>
     <row r="1803" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1803" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C1803" s="2">
         <v>1090411</v>
@@ -26689,7 +26690,7 @@
     </row>
     <row r="1804" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1804" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C1804" s="2">
         <v>1070301</v>
@@ -26703,13 +26704,13 @@
     </row>
     <row r="1805" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1805" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C1805" s="2">
         <v>1030207</v>
       </c>
       <c r="D1805" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E1805">
         <v>50.3</v>
@@ -26717,13 +26718,13 @@
     </row>
     <row r="1806" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1806" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C1806" s="2">
         <v>1040201</v>
       </c>
       <c r="D1806" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E1806">
         <v>18.8</v>
@@ -26731,13 +26732,13 @@
     </row>
     <row r="1807" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1807" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C1807" s="2">
         <v>1700031</v>
       </c>
       <c r="D1807" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E1807">
         <v>12.6</v>
@@ -26745,13 +26746,13 @@
     </row>
     <row r="1808" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1808" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C1808" s="2">
         <v>1030206</v>
       </c>
       <c r="D1808" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E1808">
         <v>7.56</v>
@@ -26759,7 +26760,7 @@
     </row>
     <row r="1809" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1809" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C1809" s="2">
         <v>1020301</v>
@@ -26773,7 +26774,7 @@
     </row>
     <row r="1810" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1810" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C1810" s="2">
         <v>1090211</v>
@@ -26787,7 +26788,7 @@
     </row>
     <row r="1811" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1811" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C1811" s="2">
         <v>1090701</v>
@@ -26801,7 +26802,7 @@
     </row>
     <row r="1812" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1812" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C1812" s="2">
         <v>1080201</v>
@@ -26815,13 +26816,13 @@
     </row>
     <row r="1813" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1813" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C1813" s="2">
         <v>1090321</v>
       </c>
       <c r="D1813" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E1813">
         <v>0.01</v>
@@ -26829,7 +26830,7 @@
     </row>
     <row r="1814" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1814" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C1814" s="2">
         <v>1090301</v>
@@ -26843,7 +26844,7 @@
     </row>
     <row r="1815" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1815" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C1815" s="2">
         <v>1090311</v>
@@ -26857,13 +26858,13 @@
     </row>
     <row r="1816" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1816" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C1816" s="2">
         <v>1030207</v>
       </c>
       <c r="D1816" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E1816">
         <v>48</v>
@@ -26871,13 +26872,13 @@
     </row>
     <row r="1817" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1817" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C1817" s="2">
         <v>1040201</v>
       </c>
       <c r="D1817" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E1817">
         <v>18</v>
@@ -26885,13 +26886,13 @@
     </row>
     <row r="1818" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1818" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C1818" s="2">
         <v>1700031</v>
       </c>
       <c r="D1818" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E1818">
         <v>12</v>
@@ -26899,13 +26900,13 @@
     </row>
     <row r="1819" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1819" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C1819" s="2">
         <v>1030206</v>
       </c>
       <c r="D1819" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E1819">
         <v>7.7</v>
@@ -26913,7 +26914,7 @@
     </row>
     <row r="1820" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1820" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C1820" s="2">
         <v>1020301</v>
@@ -26927,7 +26928,7 @@
     </row>
     <row r="1821" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1821" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C1821" s="2">
         <v>1060441</v>
@@ -26941,7 +26942,7 @@
     </row>
     <row r="1822" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1822" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C1822" s="2">
         <v>1700005</v>
@@ -26955,7 +26956,7 @@
     </row>
     <row r="1823" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1823" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C1823" s="2">
         <v>1080201</v>
@@ -26969,13 +26970,13 @@
     </row>
     <row r="1824" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1824" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C1824" s="2">
         <v>1090321</v>
       </c>
       <c r="D1824" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E1824">
         <v>0.01</v>
@@ -26983,7 +26984,7 @@
     </row>
     <row r="1825" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1825" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C1825" s="2">
         <v>1090301</v>
@@ -26997,7 +26998,7 @@
     </row>
     <row r="1826" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1826" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C1826" s="2">
         <v>1090311</v>
@@ -27011,13 +27012,13 @@
     </row>
     <row r="1827" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1827" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C1827" s="2">
         <v>1030207</v>
       </c>
       <c r="D1827" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E1827">
         <v>48.5</v>
@@ -27025,13 +27026,13 @@
     </row>
     <row r="1828" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1828" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C1828" s="2">
         <v>1040201</v>
       </c>
       <c r="D1828" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E1828">
         <v>18.2</v>
@@ -27039,13 +27040,13 @@
     </row>
     <row r="1829" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1829" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C1829" s="2">
         <v>1700031</v>
       </c>
       <c r="D1829" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E1829">
         <v>12.1</v>
@@ -27053,13 +27054,13 @@
     </row>
     <row r="1830" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1830" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C1830" s="2">
         <v>1030206</v>
       </c>
       <c r="D1830" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E1830">
         <v>7.3</v>
@@ -27067,7 +27068,7 @@
     </row>
     <row r="1831" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1831" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C1831" s="2">
         <v>1020301</v>
@@ -27081,13 +27082,13 @@
     </row>
     <row r="1832" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1832" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C1832" s="2">
         <v>1700036</v>
       </c>
       <c r="D1832" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E1832">
         <v>4.75</v>
@@ -27095,7 +27096,7 @@
     </row>
     <row r="1833" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1833" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C1833" s="2">
         <v>1060412</v>
@@ -27109,7 +27110,7 @@
     </row>
     <row r="1834" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1834" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C1834" s="2">
         <v>1080201</v>
@@ -27123,13 +27124,13 @@
     </row>
     <row r="1835" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1835" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C1835" s="2">
         <v>1090321</v>
       </c>
       <c r="D1835" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E1835">
         <v>0.01</v>
@@ -27137,7 +27138,7 @@
     </row>
     <row r="1836" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1836" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C1836" s="2">
         <v>1090301</v>
@@ -27151,7 +27152,7 @@
     </row>
     <row r="1837" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1837" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C1837" s="2">
         <v>1090311</v>
@@ -27165,13 +27166,13 @@
     </row>
     <row r="1838" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1838" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C1838" s="2">
         <v>1010601</v>
       </c>
       <c r="D1838" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E1838">
         <v>19.817</v>
@@ -27179,7 +27180,7 @@
     </row>
     <row r="1839" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1839" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C1839" s="2">
         <v>1040201</v>
@@ -27193,13 +27194,13 @@
     </row>
     <row r="1840" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1840" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C1840" s="2">
         <v>1600101</v>
       </c>
       <c r="D1840" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E1840">
         <v>18.54</v>
@@ -27207,13 +27208,13 @@
     </row>
     <row r="1841" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1841" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C1841" s="2">
         <v>1030207</v>
       </c>
       <c r="D1841" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E1841">
         <v>12.760999999999999</v>
@@ -27221,13 +27222,13 @@
     </row>
     <row r="1842" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1842" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C1842" s="2">
         <v>1060451</v>
       </c>
       <c r="D1842" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E1842">
         <v>7</v>
@@ -27235,13 +27236,13 @@
     </row>
     <row r="1843" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1843" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C1843" s="2">
         <v>1600112</v>
       </c>
       <c r="D1843" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E1843">
         <v>4.7</v>
@@ -27249,7 +27250,7 @@
     </row>
     <row r="1844" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1844" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C1844" s="2">
         <v>1030601</v>
@@ -27263,7 +27264,7 @@
     </row>
     <row r="1845" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1845" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C1845" s="2">
         <v>1020401</v>
@@ -27277,7 +27278,7 @@
     </row>
     <row r="1846" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1846" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C1846" s="2">
         <v>1050541</v>
@@ -27291,7 +27292,7 @@
     </row>
     <row r="1847" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1847" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C1847" s="2">
         <v>1700005</v>
@@ -27305,7 +27306,7 @@
     </row>
     <row r="1848" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1848" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C1848" s="2">
         <v>1060441</v>
@@ -27319,7 +27320,7 @@
     </row>
     <row r="1849" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1849" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C1849" s="2">
         <v>1020301</v>
@@ -27333,7 +27334,7 @@
     </row>
     <row r="1850" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1850" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C1850" s="2">
         <v>1020201</v>
@@ -27347,7 +27348,7 @@
     </row>
     <row r="1851" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1851" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C1851" s="2">
         <v>1080201</v>
@@ -27361,7 +27362,7 @@
     </row>
     <row r="1852" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1852" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C1852" s="2">
         <v>1091001</v>
@@ -27375,13 +27376,13 @@
     </row>
     <row r="1853" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1853" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C1853" s="2">
         <v>1030205</v>
       </c>
       <c r="D1853" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E1853">
         <v>0.23499999999999999</v>
@@ -27389,7 +27390,7 @@
     </row>
     <row r="1854" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1854" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C1854" s="2">
         <v>1090411</v>
@@ -27403,7 +27404,7 @@
     </row>
     <row r="1855" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1855" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C1855" s="2">
         <v>1090301</v>
@@ -27417,7 +27418,7 @@
     </row>
     <row r="1856" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1856" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C1856" s="2">
         <v>1090321</v>
@@ -27431,7 +27432,7 @@
     </row>
     <row r="1857" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1857" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C1857" s="2">
         <v>1090311</v>
@@ -27445,13 +27446,13 @@
     </row>
     <row r="1858" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1858" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C1858" s="2">
         <v>1010601</v>
       </c>
       <c r="D1858" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E1858">
         <v>19.816600000000001</v>
@@ -27459,13 +27460,13 @@
     </row>
     <row r="1859" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1859" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C1859" s="2">
         <v>1600101</v>
       </c>
       <c r="D1859" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E1859">
         <v>19.5824</v>
@@ -27473,7 +27474,7 @@
     </row>
     <row r="1860" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1860" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C1860" s="2">
         <v>1040201</v>
@@ -27487,13 +27488,13 @@
     </row>
     <row r="1861" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1861" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C1861" s="2">
         <v>1030207</v>
       </c>
       <c r="D1861" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E1861">
         <v>17.8506</v>
@@ -27501,13 +27502,13 @@
     </row>
     <row r="1862" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1862" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C1862" s="2">
         <v>1600112</v>
       </c>
       <c r="D1862" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E1862">
         <v>4.6996000000000002</v>
@@ -27515,7 +27516,7 @@
     </row>
     <row r="1863" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1863" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C1863" s="2">
         <v>1030601</v>
@@ -27529,7 +27530,7 @@
     </row>
     <row r="1864" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1864" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C1864" s="2">
         <v>1700005</v>
@@ -27543,7 +27544,7 @@
     </row>
     <row r="1865" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1865" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C1865" s="2">
         <v>1020401</v>
@@ -27557,7 +27558,7 @@
     </row>
     <row r="1866" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1866" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C1866" s="2">
         <v>1060441</v>
@@ -27571,7 +27572,7 @@
     </row>
     <row r="1867" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1867" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C1867" s="2">
         <v>1020301</v>
@@ -27585,7 +27586,7 @@
     </row>
     <row r="1868" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1868" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C1868" s="2">
         <v>1020201</v>
@@ -27599,7 +27600,7 @@
     </row>
     <row r="1869" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1869" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C1869" s="2">
         <v>1050541</v>
@@ -27613,7 +27614,7 @@
     </row>
     <row r="1870" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1870" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C1870" s="2">
         <v>1080201</v>
@@ -27627,7 +27628,7 @@
     </row>
     <row r="1871" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1871" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C1871" s="2">
         <v>1091001</v>
@@ -27641,13 +27642,13 @@
     </row>
     <row r="1872" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1872" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C1872" s="2">
         <v>1030205</v>
       </c>
       <c r="D1872" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E1872">
         <v>0.23499999999999999</v>
@@ -27655,7 +27656,7 @@
     </row>
     <row r="1873" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1873" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C1873" s="2">
         <v>1090411</v>
@@ -27669,7 +27670,7 @@
     </row>
     <row r="1874" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1874" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C1874" s="2">
         <v>1090301</v>
@@ -27683,7 +27684,7 @@
     </row>
     <row r="1875" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1875" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C1875" s="2">
         <v>1090321</v>
@@ -27697,7 +27698,7 @@
     </row>
     <row r="1876" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1876" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C1876" s="2">
         <v>1090311</v>
@@ -27729,13 +27730,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>302</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -27746,7 +27747,7 @@
         <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D2">
         <v>2</v>
@@ -27785,7 +27786,7 @@
         <v>99</v>
       </c>
       <c r="B5" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C5" t="s">
         <v>100</v>
@@ -27799,7 +27800,7 @@
         <v>154</v>
       </c>
       <c r="B6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C6" t="s">
         <v>100</v>
@@ -27880,13 +27881,13 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>289</v>
+      </c>
+      <c r="B12" t="s">
         <v>290</v>
       </c>
-      <c r="B12" t="s">
-        <v>291</v>
-      </c>
       <c r="C12" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -27956,7 +27957,7 @@
         <v>96</v>
       </c>
       <c r="C17" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D17">
         <v>2</v>
@@ -27984,7 +27985,7 @@
         <v>148</v>
       </c>
       <c r="C19" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D19">
         <v>2</v>
@@ -28006,13 +28007,13 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>297</v>
+      </c>
+      <c r="B21" t="s">
         <v>298</v>
       </c>
-      <c r="B21" t="s">
-        <v>299</v>
-      </c>
       <c r="C21" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -28020,13 +28021,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>281</v>
+      </c>
+      <c r="B22" t="s">
         <v>282</v>
       </c>
-      <c r="B22" t="s">
-        <v>283</v>
-      </c>
       <c r="C22" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -28034,13 +28035,13 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>276</v>
+      </c>
+      <c r="B23" t="s">
         <v>277</v>
       </c>
-      <c r="B23" t="s">
-        <v>278</v>
-      </c>
       <c r="C23" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -28054,7 +28055,7 @@
         <v>192</v>
       </c>
       <c r="C24" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D24">
         <v>2</v>
@@ -28068,7 +28069,7 @@
         <v>194</v>
       </c>
       <c r="C25" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D25">
         <v>2</v>
@@ -28096,7 +28097,7 @@
         <v>11</v>
       </c>
       <c r="C27" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D27">
         <v>2</v>
@@ -28124,7 +28125,7 @@
         <v>84</v>
       </c>
       <c r="C29" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D29">
         <v>3</v>
@@ -28230,13 +28231,13 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>260</v>
+      </c>
+      <c r="B37" t="s">
         <v>261</v>
       </c>
-      <c r="B37" t="s">
-        <v>262</v>
-      </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -28244,13 +28245,13 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>262</v>
+      </c>
+      <c r="B38" t="s">
         <v>263</v>
       </c>
-      <c r="B38" t="s">
-        <v>264</v>
-      </c>
       <c r="C38" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D38">
         <v>1</v>
@@ -28258,13 +28259,13 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>258</v>
+      </c>
+      <c r="B39" t="s">
         <v>259</v>
       </c>
-      <c r="B39" t="s">
-        <v>260</v>
-      </c>
       <c r="C39" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -28272,13 +28273,13 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>268</v>
+      </c>
+      <c r="B40" t="s">
         <v>269</v>
       </c>
-      <c r="B40" t="s">
-        <v>270</v>
-      </c>
       <c r="C40" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -28286,13 +28287,13 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>265</v>
+      </c>
+      <c r="B41" t="s">
         <v>266</v>
       </c>
-      <c r="B41" t="s">
-        <v>267</v>
-      </c>
       <c r="C41" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -28306,7 +28307,7 @@
         <v>51</v>
       </c>
       <c r="C42" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D42">
         <v>2</v>
@@ -28320,7 +28321,7 @@
         <v>62</v>
       </c>
       <c r="C43" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D43">
         <v>2</v>
@@ -28334,7 +28335,7 @@
         <v>13</v>
       </c>
       <c r="C44" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D44">
         <v>2</v>
@@ -28362,7 +28363,7 @@
         <v>137</v>
       </c>
       <c r="C46" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D46">
         <v>2</v>
@@ -28376,7 +28377,7 @@
         <v>7</v>
       </c>
       <c r="C47" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D47">
         <v>2</v>
@@ -28432,7 +28433,7 @@
         <v>68</v>
       </c>
       <c r="C51" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D51">
         <v>3</v>
@@ -28468,13 +28469,13 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
+        <v>293</v>
+      </c>
+      <c r="B54" t="s">
         <v>294</v>
       </c>
-      <c r="B54" t="s">
-        <v>295</v>
-      </c>
       <c r="C54" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -28488,7 +28489,7 @@
         <v>55</v>
       </c>
       <c r="C55" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D55">
         <v>2</v>
@@ -28502,7 +28503,7 @@
         <v>59</v>
       </c>
       <c r="C56" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D56">
         <v>2</v>
@@ -28516,7 +28517,7 @@
         <v>45</v>
       </c>
       <c r="C57" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D57">
         <v>2</v>
@@ -28530,7 +28531,7 @@
         <v>57</v>
       </c>
       <c r="C58" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D58">
         <v>3</v>
@@ -28572,7 +28573,7 @@
         <v>29</v>
       </c>
       <c r="C61" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D61">
         <v>2</v>
@@ -28600,7 +28601,7 @@
         <v>23</v>
       </c>
       <c r="C63" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D63">
         <v>2</v>
@@ -28642,7 +28643,7 @@
         <v>47</v>
       </c>
       <c r="C66" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D66">
         <v>3</v>
@@ -28656,7 +28657,7 @@
         <v>49</v>
       </c>
       <c r="C67" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D67">
         <v>3</v>
@@ -28740,7 +28741,7 @@
         <v>198</v>
       </c>
       <c r="C73" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D73">
         <v>2</v>
@@ -28754,7 +28755,7 @@
         <v>97</v>
       </c>
       <c r="C74" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D74">
         <v>3</v>
@@ -28768,7 +28769,7 @@
         <v>53</v>
       </c>
       <c r="C75" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D75">
         <v>2</v>
@@ -28782,7 +28783,7 @@
         <v>91</v>
       </c>
       <c r="C76" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D76">
         <v>3</v>
@@ -28810,7 +28811,7 @@
         <v>143</v>
       </c>
       <c r="C78" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D78">
         <v>2</v>
@@ -28824,7 +28825,7 @@
         <v>181</v>
       </c>
       <c r="C79" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D79">
         <v>2</v>
@@ -28838,7 +28839,7 @@
         <v>33</v>
       </c>
       <c r="C80" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D80">
         <v>2</v>
@@ -28852,7 +28853,7 @@
         <v>19</v>
       </c>
       <c r="C81" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D81">
         <v>2</v>
@@ -28944,13 +28945,13 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
+        <v>252</v>
+      </c>
+      <c r="B88" t="s">
         <v>253</v>
       </c>
-      <c r="B88" t="s">
-        <v>254</v>
-      </c>
       <c r="C88" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -28958,13 +28959,13 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
+        <v>254</v>
+      </c>
+      <c r="B89" t="s">
         <v>255</v>
       </c>
-      <c r="B89" t="s">
-        <v>256</v>
-      </c>
       <c r="C89" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D89">
         <v>1</v>
@@ -29000,13 +29001,13 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
+        <v>271</v>
+      </c>
+      <c r="B92" t="s">
         <v>272</v>
       </c>
-      <c r="B92" t="s">
-        <v>273</v>
-      </c>
       <c r="C92" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -29014,13 +29015,13 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
+        <v>273</v>
+      </c>
+      <c r="B93" t="s">
         <v>274</v>
       </c>
-      <c r="B93" t="s">
-        <v>275</v>
-      </c>
       <c r="C93" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D93">
         <v>1</v>
@@ -29028,13 +29029,13 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
+        <v>291</v>
+      </c>
+      <c r="B94" t="s">
         <v>292</v>
       </c>
-      <c r="B94" t="s">
-        <v>293</v>
-      </c>
       <c r="C94" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -29042,13 +29043,13 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
+        <v>295</v>
+      </c>
+      <c r="B95" t="s">
         <v>296</v>
       </c>
-      <c r="B95" t="s">
-        <v>297</v>
-      </c>
       <c r="C95" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D95">
         <v>1</v>
@@ -29076,7 +29077,7 @@
         <v>126</v>
       </c>
       <c r="C97" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D97">
         <v>2</v>
@@ -29084,13 +29085,13 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
+        <v>279</v>
+      </c>
+      <c r="B98" t="s">
         <v>280</v>
       </c>
-      <c r="B98" t="s">
-        <v>281</v>
-      </c>
       <c r="C98" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -29098,13 +29099,13 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
+        <v>286</v>
+      </c>
+      <c r="B99" t="s">
         <v>287</v>
       </c>
-      <c r="B99" t="s">
-        <v>288</v>
-      </c>
       <c r="C99" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D99">
         <v>1</v>
@@ -29132,7 +29133,7 @@
         <v>79</v>
       </c>
       <c r="C101" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D101">
         <v>2</v>
